--- a/catalog/evidence/normal-chat-t04-output-copilot-20260910.xlsx
+++ b/catalog/evidence/normal-chat-t04-output-copilot-20260910.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuki\ai-prompts\catalog\evidence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E09F75F8-5C50-4C77-A5FB-61DEF779F233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDFC9BAE-9A70-4CD0-9C31-44CEE982AAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0C1695EA-EEC1-4667-BD04-DA472C3893B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1793AC02-CF62-4569-A717-ED984B126728}"/>
   </bookViews>
   <sheets>
-    <sheet name="t04-filtered-copilot-20260910" sheetId="1" r:id="rId1"/>
+    <sheet name="t04-filtered" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211ED4F6-8CB0-4CAF-A0CB-FDC50BAA8DB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FB9F92-224D-4DC0-85A1-8AA775D1006A}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
